--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N4_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N4_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>46.83538094765652</v>
+        <v>7.610749403994184</v>
       </c>
       <c r="D2" t="n">
-        <v>46.0603401345574</v>
+        <v>7.484805271865578</v>
       </c>
       <c r="E2" t="n">
-        <v>5.058469778235771</v>
+        <v>0.8220013389633127</v>
       </c>
       <c r="F2" t="n">
-        <v>5.481280080797443</v>
+        <v>0.8907080131295841</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>56.95232050412806</v>
+        <v>9.25475208192081</v>
       </c>
       <c r="D3" t="n">
-        <v>57.02290029615229</v>
+        <v>9.266221298124746</v>
       </c>
       <c r="E3" t="n">
-        <v>5.058469778235771</v>
+        <v>0.8220013389633127</v>
       </c>
       <c r="F3" t="n">
-        <v>5.481280080797443</v>
+        <v>0.8907080131295841</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
